--- a/www/flightdata/xlsx/eoss-395.xlsx
+++ b/www/flightdata/xlsx/eoss-395.xlsx
@@ -3258,7 +3258,7 @@
         <v>46124.31166375</v>
       </c>
       <c r="D2" s="1">
-        <v>46124.561631944445</v>
+        <v>46124.311631944445</v>
       </c>
       <c r="E2">
         <v>5211</v>
@@ -3365,7 +3365,7 @@
         <v>46124.31203857639</v>
       </c>
       <c r="D3" s="1">
-        <v>46124.56196759259</v>
+        <v>46124.31196759259</v>
       </c>
       <c r="E3">
         <v>5236</v>
@@ -3496,7 +3496,7 @@
         <v>46124.31201152778</v>
       </c>
       <c r="D4" s="1">
-        <v>46124.56197916667</v>
+        <v>46124.31197916667</v>
       </c>
       <c r="E4">
         <v>5312</v>
@@ -3639,7 +3639,7 @@
         <v>46124.31234810185</v>
       </c>
       <c r="D5" s="1">
-        <v>46124.56232638889</v>
+        <v>46124.31232638889</v>
       </c>
       <c r="E5">
         <v>5909</v>
@@ -3782,7 +3782,7 @@
         <v>46124.31271929398</v>
       </c>
       <c r="D6" s="1">
-        <v>46124.56266203704</v>
+        <v>46124.31266203704</v>
       </c>
       <c r="E6">
         <v>6412</v>
@@ -3925,7 +3925,7 @@
         <v>46124.31269583333</v>
       </c>
       <c r="D7" s="1">
-        <v>46124.56267361111</v>
+        <v>46124.31267361111</v>
       </c>
       <c r="E7">
         <v>6512</v>
@@ -4068,7 +4068,7 @@
         <v>46124.31304234954</v>
       </c>
       <c r="D8" s="1">
-        <v>46124.56302083333</v>
+        <v>46124.31302083333</v>
       </c>
       <c r="E8">
         <v>7100</v>
@@ -4211,7 +4211,7 @@
         <v>46124.313412881944</v>
       </c>
       <c r="D9" s="1">
-        <v>46124.56335648148</v>
+        <v>46124.31335648148</v>
       </c>
       <c r="E9">
         <v>7590</v>
@@ -4354,7 +4354,7 @@
         <v>46124.31338947917</v>
       </c>
       <c r="D10" s="1">
-        <v>46124.563368055555</v>
+        <v>46124.313368055555</v>
       </c>
       <c r="E10">
         <v>7697</v>
@@ -4497,7 +4497,7 @@
         <v>46124.31373800926</v>
       </c>
       <c r="D11" s="1">
-        <v>46124.56371527778</v>
+        <v>46124.31371527778</v>
       </c>
       <c r="E11">
         <v>8307</v>
@@ -4640,7 +4640,7 @@
         <v>46124.31410725694</v>
       </c>
       <c r="D12" s="1">
-        <v>46124.564050925925</v>
+        <v>46124.314050925925</v>
       </c>
       <c r="E12">
         <v>8761</v>
@@ -4783,7 +4783,7 @@
         <v>46124.31408561343</v>
       </c>
       <c r="D13" s="1">
-        <v>46124.5640625</v>
+        <v>46124.3140625</v>
       </c>
       <c r="E13">
         <v>8862</v>
@@ -4926,7 +4926,7 @@
         <v>46124.31443503472</v>
       </c>
       <c r="D14" s="1">
-        <v>46124.564409722225</v>
+        <v>46124.314409722225</v>
       </c>
       <c r="E14">
         <v>9433</v>
@@ -5069,7 +5069,7 @@
         <v>46124.31480425926</v>
       </c>
       <c r="D15" s="1">
-        <v>46124.56474537037</v>
+        <v>46124.31474537037</v>
       </c>
       <c r="E15">
         <v>9919</v>
@@ -5212,7 +5212,7 @@
         <v>46124.31478685185</v>
       </c>
       <c r="D16" s="1">
-        <v>46124.56475694444</v>
+        <v>46124.31475694444</v>
       </c>
       <c r="E16">
         <v>10022</v>
@@ -5355,7 +5355,7 @@
         <v>46124.31513769676</v>
       </c>
       <c r="D17" s="1">
-        <v>46124.565104166664</v>
+        <v>46124.315104166664</v>
       </c>
       <c r="E17">
         <v>10613</v>
@@ -5498,7 +5498,7 @@
         <v>46124.31549703704</v>
       </c>
       <c r="D18" s="1">
-        <v>46124.56543981482</v>
+        <v>46124.31543981482</v>
       </c>
       <c r="E18">
         <v>11099</v>
@@ -5641,7 +5641,7 @@
         <v>46124.31548611111</v>
       </c>
       <c r="D19" s="1">
-        <v>46124.56545138889</v>
+        <v>46124.31545138889</v>
       </c>
       <c r="E19">
         <v>11206</v>
@@ -5784,7 +5784,7 @@
         <v>46124.31582045139</v>
       </c>
       <c r="D20" s="1">
-        <v>46124.56579861111</v>
+        <v>46124.31579861111</v>
       </c>
       <c r="E20">
         <v>11782</v>
@@ -5927,7 +5927,7 @@
         <v>46124.316191377315</v>
       </c>
       <c r="D21" s="1">
-        <v>46124.56613425926</v>
+        <v>46124.31613425926</v>
       </c>
       <c r="E21">
         <v>12263</v>
@@ -6073,7 +6073,7 @@
         <v>46124.316168101854</v>
       </c>
       <c r="D22" s="1">
-        <v>46124.566145833334</v>
+        <v>46124.316145833334</v>
       </c>
       <c r="E22">
         <v>12364</v>
@@ -6216,7 +6216,7 @@
         <v>46124.316514398146</v>
       </c>
       <c r="D23" s="1">
-        <v>46124.56649305556</v>
+        <v>46124.31649305556</v>
       </c>
       <c r="E23">
         <v>12998</v>
@@ -6359,7 +6359,7 @@
         <v>46124.31688572917</v>
       </c>
       <c r="D24" s="1">
-        <v>46124.566828703704</v>
+        <v>46124.316828703704</v>
       </c>
       <c r="E24">
         <v>13551</v>
@@ -6502,7 +6502,7 @@
         <v>46124.31686248843</v>
       </c>
       <c r="D25" s="1">
-        <v>46124.56684027778</v>
+        <v>46124.31684027778</v>
       </c>
       <c r="E25">
         <v>13659</v>
@@ -6645,7 +6645,7 @@
         <v>46124.31720884259</v>
       </c>
       <c r="D26" s="1">
-        <v>46124.5671875</v>
+        <v>46124.3171875</v>
       </c>
       <c r="E26">
         <v>14313</v>
@@ -6788,7 +6788,7 @@
         <v>46124.31827474537</v>
       </c>
       <c r="D27" s="1">
-        <v>46124.56821759259</v>
+        <v>46124.31821759259</v>
       </c>
       <c r="E27">
         <v>16148</v>
@@ -6931,7 +6931,7 @@
         <v>46124.318250185184</v>
       </c>
       <c r="D28" s="1">
-        <v>46124.56822916667</v>
+        <v>46124.31822916667</v>
       </c>
       <c r="E28">
         <v>16255</v>
@@ -7074,7 +7074,7 @@
         <v>46124.318969803244</v>
       </c>
       <c r="D29" s="1">
-        <v>46124.56891203704</v>
+        <v>46124.31891203704</v>
       </c>
       <c r="E29">
         <v>17428</v>
@@ -7217,7 +7217,7 @@
         <v>46124.31894462963</v>
       </c>
       <c r="D30" s="1">
-        <v>46124.568923611114</v>
+        <v>46124.318923611114</v>
       </c>
       <c r="E30">
         <v>17565</v>
@@ -7360,7 +7360,7 @@
         <v>46124.3193075463</v>
       </c>
       <c r="D31" s="1">
-        <v>46124.56927083333</v>
+        <v>46124.31927083333</v>
       </c>
       <c r="E31">
         <v>18275</v>
@@ -7503,7 +7503,7 @@
         <v>46124.319664456016</v>
       </c>
       <c r="D32" s="1">
-        <v>46124.569606481484</v>
+        <v>46124.319606481484</v>
       </c>
       <c r="E32">
         <v>18854</v>
@@ -7646,7 +7646,7 @@
         <v>46124.31964005787</v>
       </c>
       <c r="D33" s="1">
-        <v>46124.56961805555</v>
+        <v>46124.31961805555</v>
       </c>
       <c r="E33">
         <v>18987</v>
@@ -7789,7 +7789,7 @@
         <v>46124.31998748842</v>
       </c>
       <c r="D34" s="1">
-        <v>46124.56996527778</v>
+        <v>46124.31996527778</v>
       </c>
       <c r="E34">
         <v>19675</v>
@@ -7932,7 +7932,7 @@
         <v>46124.32033335648</v>
       </c>
       <c r="D35" s="1">
-        <v>46124.5703125</v>
+        <v>46124.3203125</v>
       </c>
       <c r="E35">
         <v>20370</v>
@@ -8075,7 +8075,7 @@
         <v>46124.320698171294</v>
       </c>
       <c r="D36" s="1">
-        <v>46124.57065972222</v>
+        <v>46124.32065972222</v>
       </c>
       <c r="E36">
         <v>21048</v>
@@ -8218,7 +8218,7 @@
         <v>46124.32105337963</v>
       </c>
       <c r="D37" s="1">
-        <v>46124.57099537037</v>
+        <v>46124.32099537037</v>
       </c>
       <c r="E37">
         <v>21648</v>
@@ -8361,7 +8361,7 @@
         <v>46124.32102974537</v>
       </c>
       <c r="D38" s="1">
-        <v>46124.57100694445</v>
+        <v>46124.32100694445</v>
       </c>
       <c r="E38">
         <v>21752</v>
@@ -8504,7 +8504,7 @@
         <v>46124.32137697917</v>
       </c>
       <c r="D39" s="1">
-        <v>46124.57135416667</v>
+        <v>46124.32135416667</v>
       </c>
       <c r="E39">
         <v>22404</v>
@@ -8647,7 +8647,7 @@
         <v>46124.32174817129</v>
       </c>
       <c r="D40" s="1">
-        <v>46124.57168981482</v>
+        <v>46124.32168981482</v>
       </c>
       <c r="E40">
         <v>23006</v>
@@ -8790,7 +8790,7 @@
         <v>46124.32172864583</v>
       </c>
       <c r="D41" s="1">
-        <v>46124.571701388886</v>
+        <v>46124.321701388886</v>
       </c>
       <c r="E41">
         <v>23110</v>
@@ -8933,7 +8933,7 @@
         <v>46124.3220762037</v>
       </c>
       <c r="D42" s="1">
-        <v>46124.57204861111</v>
+        <v>46124.32204861111</v>
       </c>
       <c r="E42">
         <v>23862</v>
@@ -9076,7 +9076,7 @@
         <v>46124.322442337965</v>
       </c>
       <c r="D43" s="1">
-        <v>46124.572384259256</v>
+        <v>46124.322384259256</v>
       </c>
       <c r="E43">
         <v>24487</v>
@@ -9219,7 +9219,7 @@
         <v>46124.32241851852</v>
       </c>
       <c r="D44" s="1">
-        <v>46124.57239583333</v>
+        <v>46124.32239583333</v>
       </c>
       <c r="E44">
         <v>24595</v>
@@ -9362,7 +9362,7 @@
         <v>46124.32276510417</v>
       </c>
       <c r="D45" s="1">
-        <v>46124.572743055556</v>
+        <v>46124.322743055556</v>
       </c>
       <c r="E45">
         <v>25269</v>
@@ -9505,7 +9505,7 @@
         <v>46124.32313645833</v>
       </c>
       <c r="D46" s="1">
-        <v>46124.5730787037</v>
+        <v>46124.3230787037</v>
       </c>
       <c r="E46">
         <v>25824</v>
@@ -9648,7 +9648,7 @@
         <v>46124.32311158565</v>
       </c>
       <c r="D47" s="1">
-        <v>46124.57309027778</v>
+        <v>46124.32309027778</v>
       </c>
       <c r="E47">
         <v>25927</v>
@@ -9791,7 +9791,7 @@
         <v>46124.32346255787</v>
       </c>
       <c r="D48" s="1">
-        <v>46124.5734375</v>
+        <v>46124.3234375</v>
       </c>
       <c r="E48">
         <v>26601</v>
@@ -9934,7 +9934,7 @@
         <v>46124.32383137732</v>
       </c>
       <c r="D49" s="1">
-        <v>46124.57377314815</v>
+        <v>46124.32377314815</v>
       </c>
       <c r="E49">
         <v>27216</v>
@@ -10077,7 +10077,7 @@
         <v>46124.32380976852</v>
       </c>
       <c r="D50" s="1">
-        <v>46124.57378472222</v>
+        <v>46124.32378472222</v>
       </c>
       <c r="E50">
         <v>27328</v>
@@ -10220,7 +10220,7 @@
         <v>46124.32415368056</v>
       </c>
       <c r="D51" s="1">
-        <v>46124.57413194444</v>
+        <v>46124.32413194444</v>
       </c>
       <c r="E51">
         <v>27994</v>
@@ -10363,7 +10363,7 @@
         <v>46124.32452678241</v>
       </c>
       <c r="D52" s="1">
-        <v>46124.574467592596</v>
+        <v>46124.324467592596</v>
       </c>
       <c r="E52">
         <v>28634</v>
@@ -10506,7 +10506,7 @@
         <v>46124.32450052083</v>
       </c>
       <c r="D53" s="1">
-        <v>46124.574479166666</v>
+        <v>46124.324479166666</v>
       </c>
       <c r="E53">
         <v>28743</v>
@@ -10649,7 +10649,7 @@
         <v>46124.32484825231</v>
       </c>
       <c r="D54" s="1">
-        <v>46124.57482638889</v>
+        <v>46124.32482638889</v>
       </c>
       <c r="E54">
         <v>29495</v>
@@ -10792,7 +10792,7 @@
         <v>46124.32522099537</v>
       </c>
       <c r="D55" s="1">
-        <v>46124.575162037036</v>
+        <v>46124.325162037036</v>
       </c>
       <c r="E55">
         <v>30114</v>
@@ -10935,7 +10935,7 @@
         <v>46124.32519645833</v>
       </c>
       <c r="D56" s="1">
-        <v>46124.57517361111</v>
+        <v>46124.32517361111</v>
       </c>
       <c r="E56">
         <v>30222</v>
@@ -11078,7 +11078,7 @@
         <v>46124.32554268518</v>
       </c>
       <c r="D57" s="1">
-        <v>46124.575520833336</v>
+        <v>46124.325520833336</v>
       </c>
       <c r="E57">
         <v>30923</v>
@@ -11221,7 +11221,7 @@
         <v>46124.325914270834</v>
       </c>
       <c r="D58" s="1">
-        <v>46124.57585648148</v>
+        <v>46124.32585648148</v>
       </c>
       <c r="E58">
         <v>31527</v>
@@ -11364,7 +11364,7 @@
         <v>46124.32588946759</v>
       </c>
       <c r="D59" s="1">
-        <v>46124.57586805556</v>
+        <v>46124.32586805556</v>
       </c>
       <c r="E59">
         <v>31642</v>
@@ -11507,7 +11507,7 @@
         <v>46124.32623814815</v>
       </c>
       <c r="D60" s="1">
-        <v>46124.576215277775</v>
+        <v>46124.326215277775</v>
       </c>
       <c r="E60">
         <v>32428</v>
@@ -11650,7 +11650,7 @@
         <v>46124.32660908565</v>
       </c>
       <c r="D61" s="1">
-        <v>46124.57655092593</v>
+        <v>46124.32655092593</v>
       </c>
       <c r="E61">
         <v>33115</v>
@@ -11793,7 +11793,7 @@
         <v>46124.32658443287</v>
       </c>
       <c r="D62" s="1">
-        <v>46124.5765625</v>
+        <v>46124.3265625</v>
       </c>
       <c r="E62">
         <v>33230</v>
@@ -11936,7 +11936,7 @@
         <v>46124.32694385417</v>
       </c>
       <c r="D63" s="1">
-        <v>46124.576898148145</v>
+        <v>46124.326898148145</v>
       </c>
       <c r="E63">
         <v>33958</v>
@@ -12058,7 +12058,7 @@
         <v>46124.32693216435</v>
       </c>
       <c r="D64" s="1">
-        <v>46124.57690972222</v>
+        <v>46124.32690972222</v>
       </c>
       <c r="E64">
         <v>34087</v>
@@ -12201,7 +12201,7 @@
         <v>46124.32730266204</v>
       </c>
       <c r="D65" s="1">
-        <v>46124.57724537037</v>
+        <v>46124.32724537037</v>
       </c>
       <c r="E65">
         <v>34778</v>
@@ -12344,7 +12344,7 @@
         <v>46124.327279212965</v>
       </c>
       <c r="D66" s="1">
-        <v>46124.577256944445</v>
+        <v>46124.327256944445</v>
       </c>
       <c r="E66">
         <v>34893</v>
@@ -12487,7 +12487,7 @@
         <v>46124.32762644676</v>
       </c>
       <c r="D67" s="1">
-        <v>46124.57760416667</v>
+        <v>46124.32760416667</v>
       </c>
       <c r="E67">
         <v>35723</v>
@@ -12630,7 +12630,7 @@
         <v>46124.327997291664</v>
       </c>
       <c r="D68" s="1">
-        <v>46124.577939814815</v>
+        <v>46124.327939814815</v>
       </c>
       <c r="E68">
         <v>36416</v>
@@ -12773,7 +12773,7 @@
         <v>46124.327973287036</v>
       </c>
       <c r="D69" s="1">
-        <v>46124.57795138889</v>
+        <v>46124.32795138889</v>
       </c>
       <c r="E69">
         <v>36524</v>
@@ -12916,7 +12916,7 @@
         <v>46124.3283209375</v>
       </c>
       <c r="D70" s="1">
-        <v>46124.57829861111</v>
+        <v>46124.32829861111</v>
       </c>
       <c r="E70">
         <v>37333</v>
@@ -13059,7 +13059,7 @@
         <v>46124.32869336806</v>
       </c>
       <c r="D71" s="1">
-        <v>46124.57863425926</v>
+        <v>46124.32863425926</v>
       </c>
       <c r="E71">
         <v>38042</v>
@@ -13202,7 +13202,7 @@
         <v>46124.32866842593</v>
       </c>
       <c r="D72" s="1">
-        <v>46124.57864583333</v>
+        <v>46124.32864583333</v>
       </c>
       <c r="E72">
         <v>38154</v>
@@ -13345,7 +13345,7 @@
         <v>46124.32901538195</v>
       </c>
       <c r="D73" s="1">
-        <v>46124.578993055555</v>
+        <v>46124.328993055555</v>
       </c>
       <c r="E73">
         <v>38962</v>
@@ -13488,7 +13488,7 @@
         <v>46124.32938724537</v>
       </c>
       <c r="D74" s="1">
-        <v>46124.5793287037</v>
+        <v>46124.3293287037</v>
       </c>
       <c r="E74">
         <v>39697</v>
@@ -13631,7 +13631,7 @@
         <v>46124.32936232639</v>
       </c>
       <c r="D75" s="1">
-        <v>46124.57934027778</v>
+        <v>46124.32934027778</v>
       </c>
       <c r="E75">
         <v>39815</v>
@@ -13774,7 +13774,7 @@
         <v>46124.32970952546</v>
       </c>
       <c r="D76" s="1">
-        <v>46124.5796875</v>
+        <v>46124.3296875</v>
       </c>
       <c r="E76">
         <v>40701</v>
@@ -13917,7 +13917,7 @@
         <v>46124.33008231482</v>
       </c>
       <c r="D77" s="1">
-        <v>46124.58002314815</v>
+        <v>46124.33002314815</v>
       </c>
       <c r="E77">
         <v>41330</v>
@@ -14060,7 +14060,7 @@
         <v>46124.33007008102</v>
       </c>
       <c r="D78" s="1">
-        <v>46124.58002314815</v>
+        <v>46124.33002314815</v>
       </c>
       <c r="E78">
         <v>41314</v>
@@ -14182,7 +14182,7 @@
         <v>46124.330056921295</v>
       </c>
       <c r="D79" s="1">
-        <v>46124.580034722225</v>
+        <v>46124.330034722225</v>
       </c>
       <c r="E79">
         <v>41438</v>
@@ -14325,7 +14325,7 @@
         <v>46124.33040337963</v>
       </c>
       <c r="D80" s="1">
-        <v>46124.58038194444</v>
+        <v>46124.33038194444</v>
       </c>
       <c r="E80">
         <v>41929</v>
@@ -14468,7 +14468,7 @@
         <v>46124.3307750463</v>
       </c>
       <c r="D81" s="1">
-        <v>46124.580717592595</v>
+        <v>46124.330717592595</v>
       </c>
       <c r="E81">
         <v>42326</v>
@@ -14611,7 +14611,7 @@
         <v>46124.33075159722</v>
       </c>
       <c r="D82" s="1">
-        <v>46124.580729166664</v>
+        <v>46124.330729166664</v>
       </c>
       <c r="E82">
         <v>42422</v>
@@ -14754,7 +14754,7 @@
         <v>46124.33109753472</v>
       </c>
       <c r="D83" s="1">
-        <v>46124.58107638889</v>
+        <v>46124.33107638889</v>
       </c>
       <c r="E83">
         <v>42881</v>
@@ -14897,7 +14897,7 @@
         <v>46124.33146944444</v>
       </c>
       <c r="D84" s="1">
-        <v>46124.581412037034</v>
+        <v>46124.331412037034</v>
       </c>
       <c r="E84">
         <v>43312</v>
@@ -15040,7 +15040,7 @@
         <v>46124.33144646991</v>
       </c>
       <c r="D85" s="1">
-        <v>46124.58142361111</v>
+        <v>46124.33142361111</v>
       </c>
       <c r="E85">
         <v>43410</v>
@@ -15183,7 +15183,7 @@
         <v>46124.33179211806</v>
       </c>
       <c r="D86" s="1">
-        <v>46124.581770833334</v>
+        <v>46124.331770833334</v>
       </c>
       <c r="E86">
         <v>44095</v>
@@ -15326,7 +15326,7 @@
         <v>46124.33214140046</v>
       </c>
       <c r="D87" s="1">
-        <v>46124.58211805556</v>
+        <v>46124.33211805556</v>
       </c>
       <c r="E87">
         <v>44848</v>
@@ -15469,7 +15469,7 @@
         <v>46124.33248774306</v>
       </c>
       <c r="D88" s="1">
-        <v>46124.58246527778</v>
+        <v>46124.33246527778</v>
       </c>
       <c r="E88">
         <v>45560</v>
@@ -15612,7 +15612,7 @@
         <v>46124.33285946759</v>
       </c>
       <c r="D89" s="1">
-        <v>46124.58280092593</v>
+        <v>46124.33280092593</v>
       </c>
       <c r="E89">
         <v>46291</v>
@@ -15755,7 +15755,7 @@
         <v>46124.33283435185</v>
       </c>
       <c r="D90" s="1">
-        <v>46124.5828125</v>
+        <v>46124.3328125</v>
       </c>
       <c r="E90">
         <v>46402</v>
@@ -15898,7 +15898,7 @@
         <v>46124.3331859838</v>
       </c>
       <c r="D91" s="1">
-        <v>46124.58315972222</v>
+        <v>46124.33315972222</v>
       </c>
       <c r="E91">
         <v>47071</v>
@@ -16041,7 +16041,7 @@
         <v>46124.333554537036</v>
       </c>
       <c r="D92" s="1">
-        <v>46124.58349537037</v>
+        <v>46124.33349537037</v>
       </c>
       <c r="E92">
         <v>47563</v>
@@ -16184,7 +16184,7 @@
         <v>46124.33352892361</v>
       </c>
       <c r="D93" s="1">
-        <v>46124.583506944444</v>
+        <v>46124.333506944444</v>
       </c>
       <c r="E93">
         <v>47662</v>
@@ -16327,7 +16327,7 @@
         <v>46124.33387494213</v>
       </c>
       <c r="D94" s="1">
-        <v>46124.58385416667</v>
+        <v>46124.33385416667</v>
       </c>
       <c r="E94">
         <v>48083</v>
@@ -16470,7 +16470,7 @@
         <v>46124.33424847222</v>
       </c>
       <c r="D95" s="1">
-        <v>46124.584189814814</v>
+        <v>46124.334189814814</v>
       </c>
       <c r="E95">
         <v>48664</v>
@@ -16613,7 +16613,7 @@
         <v>46124.33422318287</v>
       </c>
       <c r="D96" s="1">
-        <v>46124.58420138889</v>
+        <v>46124.33420138889</v>
       </c>
       <c r="E96">
         <v>48767</v>
@@ -16756,7 +16756,7 @@
         <v>46124.334570694446</v>
       </c>
       <c r="D97" s="1">
-        <v>46124.584548611114</v>
+        <v>46124.334548611114</v>
       </c>
       <c r="E97">
         <v>49332</v>
@@ -16899,7 +16899,7 @@
         <v>46124.33494299769</v>
       </c>
       <c r="D98" s="1">
-        <v>46124.58488425926</v>
+        <v>46124.33488425926</v>
       </c>
       <c r="E98">
         <v>49894</v>
@@ -17042,7 +17042,7 @@
         <v>46124.33491760417</v>
       </c>
       <c r="D99" s="1">
-        <v>46124.58489583333</v>
+        <v>46124.33489583333</v>
       </c>
       <c r="E99">
         <v>49991</v>
@@ -17185,7 +17185,7 @@
         <v>46124.33526611111</v>
       </c>
       <c r="D100" s="1">
-        <v>46124.58524305555</v>
+        <v>46124.33524305555</v>
       </c>
       <c r="E100">
         <v>50785</v>
@@ -17328,7 +17328,7 @@
         <v>46124.33561201389</v>
       </c>
       <c r="D101" s="1">
-        <v>46124.58559027778</v>
+        <v>46124.33559027778</v>
       </c>
       <c r="E101">
         <v>51329</v>
@@ -17471,7 +17471,7 @@
         <v>46124.33595916667</v>
       </c>
       <c r="D102" s="1">
-        <v>46124.5859375</v>
+        <v>46124.3359375</v>
       </c>
       <c r="E102">
         <v>51917</v>
@@ -17614,7 +17614,7 @@
         <v>46124.336332314815</v>
       </c>
       <c r="D103" s="1">
-        <v>46124.58627314815</v>
+        <v>46124.33627314815</v>
       </c>
       <c r="E103">
         <v>52435</v>
@@ -17757,7 +17757,7 @@
         <v>46124.33630653935</v>
       </c>
       <c r="D104" s="1">
-        <v>46124.58628472222</v>
+        <v>46124.33628472222</v>
       </c>
       <c r="E104">
         <v>52534</v>
@@ -17900,7 +17900,7 @@
         <v>46124.336654189814</v>
       </c>
       <c r="D105" s="1">
-        <v>46124.58663194445</v>
+        <v>46124.33663194445</v>
       </c>
       <c r="E105">
         <v>53126</v>
@@ -18043,7 +18043,7 @@
         <v>46124.33702594908</v>
       </c>
       <c r="D106" s="1">
-        <v>46124.58696759259</v>
+        <v>46124.33696759259</v>
       </c>
       <c r="E106">
         <v>53611</v>
@@ -18186,7 +18186,7 @@
         <v>46124.337002002314</v>
       </c>
       <c r="D107" s="1">
-        <v>46124.58697916667</v>
+        <v>46124.33697916667</v>
       </c>
       <c r="E107">
         <v>53707</v>
@@ -18329,7 +18329,7 @@
         <v>46124.33735018518</v>
       </c>
       <c r="D108" s="1">
-        <v>46124.587326388886</v>
+        <v>46124.337326388886</v>
       </c>
       <c r="E108">
         <v>54300</v>
@@ -18472,7 +18472,7 @@
         <v>46124.33772146991</v>
       </c>
       <c r="D109" s="1">
-        <v>46124.58766203704</v>
+        <v>46124.33766203704</v>
       </c>
       <c r="E109">
         <v>54827</v>
@@ -18615,7 +18615,7 @@
         <v>46124.33769569444</v>
       </c>
       <c r="D110" s="1">
-        <v>46124.58767361111</v>
+        <v>46124.33767361111</v>
       </c>
       <c r="E110">
         <v>54925</v>
@@ -18758,7 +18758,7 @@
         <v>46124.338043275464</v>
       </c>
       <c r="D111" s="1">
-        <v>46124.58802083333</v>
+        <v>46124.33802083333</v>
       </c>
       <c r="E111">
         <v>55594</v>
@@ -18901,7 +18901,7 @@
         <v>46124.33841587963</v>
       </c>
       <c r="D112" s="1">
-        <v>46124.58835648148</v>
+        <v>46124.33835648148</v>
       </c>
       <c r="E112">
         <v>56139</v>
@@ -19044,7 +19044,7 @@
         <v>46124.33838902778</v>
       </c>
       <c r="D113" s="1">
-        <v>46124.588368055556</v>
+        <v>46124.338368055556</v>
       </c>
       <c r="E113">
         <v>56239</v>
@@ -19187,7 +19187,7 @@
         <v>46124.33873773148</v>
       </c>
       <c r="D114" s="1">
-        <v>46124.58871527778</v>
+        <v>46124.33871527778</v>
       </c>
       <c r="E114">
         <v>57037</v>
@@ -19330,7 +19330,7 @@
         <v>46124.339110092595</v>
       </c>
       <c r="D115" s="1">
-        <v>46124.589050925926</v>
+        <v>46124.339050925926</v>
       </c>
       <c r="E115">
         <v>57795</v>
@@ -19473,7 +19473,7 @@
         <v>46124.33908366898</v>
       </c>
       <c r="D116" s="1">
-        <v>46124.5890625</v>
+        <v>46124.3390625</v>
       </c>
       <c r="E116">
         <v>57901</v>
@@ -19616,7 +19616,7 @@
         <v>46124.33943861111</v>
       </c>
       <c r="D117" s="1">
-        <v>46124.58940972222</v>
+        <v>46124.33940972222</v>
       </c>
       <c r="E117">
         <v>58551</v>
@@ -19759,7 +19759,7 @@
         <v>46124.3398040625</v>
       </c>
       <c r="D118" s="1">
-        <v>46124.58974537037</v>
+        <v>46124.33974537037</v>
       </c>
       <c r="E118">
         <v>58985</v>
@@ -19902,7 +19902,7 @@
         <v>46124.339779560185</v>
       </c>
       <c r="D119" s="1">
-        <v>46124.58975694444</v>
+        <v>46124.33975694444</v>
       </c>
       <c r="E119">
         <v>59085</v>
@@ -20045,7 +20045,7 @@
         <v>46124.340124594906</v>
       </c>
       <c r="D120" s="1">
-        <v>46124.590104166666</v>
+        <v>46124.340104166666</v>
       </c>
       <c r="E120">
         <v>59737</v>
@@ -20188,7 +20188,7 @@
         <v>46124.34049857639</v>
       </c>
       <c r="D121" s="1">
-        <v>46124.59043981481</v>
+        <v>46124.34043981481</v>
       </c>
       <c r="E121">
         <v>60308</v>
@@ -20331,7 +20331,7 @@
         <v>46124.340473171294</v>
       </c>
       <c r="D122" s="1">
-        <v>46124.59045138889</v>
+        <v>46124.34045138889</v>
       </c>
       <c r="E122">
         <v>60409</v>
@@ -20474,7 +20474,7 @@
         <v>46124.340821261576</v>
       </c>
       <c r="D123" s="1">
-        <v>46124.59079861111</v>
+        <v>46124.34079861111</v>
       </c>
       <c r="E123">
         <v>61168</v>
@@ -20617,7 +20617,7 @@
         <v>46124.34119318287</v>
       </c>
       <c r="D124" s="1">
-        <v>46124.59113425926</v>
+        <v>46124.34113425926</v>
       </c>
       <c r="E124">
         <v>61958</v>
@@ -20760,7 +20760,7 @@
         <v>46124.34116866898</v>
       </c>
       <c r="D125" s="1">
-        <v>46124.591145833336</v>
+        <v>46124.341145833336</v>
       </c>
       <c r="E125">
         <v>62056</v>
@@ -20903,7 +20903,7 @@
         <v>46124.341515127315</v>
       </c>
       <c r="D126" s="1">
-        <v>46124.59149305556</v>
+        <v>46124.34149305556</v>
       </c>
       <c r="E126">
         <v>62685</v>
@@ -21046,7 +21046,7 @@
         <v>46124.341886712966</v>
       </c>
       <c r="D127" s="1">
-        <v>46124.591828703706</v>
+        <v>46124.341828703706</v>
       </c>
       <c r="E127">
         <v>63412</v>
@@ -21189,7 +21189,7 @@
         <v>46124.3418622338</v>
       </c>
       <c r="D128" s="1">
-        <v>46124.591840277775</v>
+        <v>46124.341840277775</v>
       </c>
       <c r="E128">
         <v>63520</v>
@@ -21332,7 +21332,7 @@
         <v>46124.342211296294</v>
       </c>
       <c r="D129" s="1">
-        <v>46124.5921875</v>
+        <v>46124.3421875</v>
       </c>
       <c r="E129">
         <v>64144</v>
@@ -21478,7 +21478,7 @@
         <v>46124.34258189815</v>
       </c>
       <c r="D130" s="1">
-        <v>46124.592523148145</v>
+        <v>46124.342523148145</v>
       </c>
       <c r="E130">
         <v>64632</v>
@@ -21621,7 +21621,7 @@
         <v>46124.342566087966</v>
       </c>
       <c r="D131" s="1">
-        <v>46124.59253472222</v>
+        <v>46124.34253472222</v>
       </c>
       <c r="E131">
         <v>64735</v>
@@ -21764,7 +21764,7 @@
         <v>46124.34290394676</v>
       </c>
       <c r="D132" s="1">
-        <v>46124.592881944445</v>
+        <v>46124.342881944445</v>
       </c>
       <c r="E132">
         <v>65279</v>
@@ -21907,7 +21907,7 @@
         <v>46124.34327604167</v>
       </c>
       <c r="D133" s="1">
-        <v>46124.59321759259</v>
+        <v>46124.34321759259</v>
       </c>
       <c r="E133">
         <v>65766</v>
@@ -22050,7 +22050,7 @@
         <v>46124.343250625</v>
       </c>
       <c r="D134" s="1">
-        <v>46124.59322916667</v>
+        <v>46124.34322916667</v>
       </c>
       <c r="E134">
         <v>65867</v>
@@ -22193,7 +22193,7 @@
         <v>46124.34359777778</v>
       </c>
       <c r="D135" s="1">
-        <v>46124.59357638889</v>
+        <v>46124.34357638889</v>
       </c>
       <c r="E135">
         <v>66348</v>
@@ -22336,7 +22336,7 @@
         <v>46124.3439715162</v>
       </c>
       <c r="D136" s="1">
-        <v>46124.59391203704</v>
+        <v>46124.34391203704</v>
       </c>
       <c r="E136">
         <v>66731</v>
@@ -22479,7 +22479,7 @@
         <v>46124.343945381945</v>
       </c>
       <c r="D137" s="1">
-        <v>46124.59392361111</v>
+        <v>46124.34392361111</v>
       </c>
       <c r="E137">
         <v>66833</v>
@@ -22622,7 +22622,7 @@
         <v>46124.34429311343</v>
       </c>
       <c r="D138" s="1">
-        <v>46124.59427083333</v>
+        <v>46124.34427083333</v>
       </c>
       <c r="E138">
         <v>67377</v>
@@ -22765,7 +22765,7 @@
         <v>46124.34464125</v>
       </c>
       <c r="D139" s="1">
-        <v>46124.594618055555</v>
+        <v>46124.344618055555</v>
       </c>
       <c r="E139">
         <v>67947</v>
@@ -22908,7 +22908,7 @@
         <v>46124.34498695602</v>
       </c>
       <c r="D140" s="1">
-        <v>46124.59496527778</v>
+        <v>46124.34496527778</v>
       </c>
       <c r="E140">
         <v>68716</v>
@@ -23051,7 +23051,7 @@
         <v>46124.34536072917</v>
       </c>
       <c r="D141" s="1">
-        <v>46124.595300925925</v>
+        <v>46124.345300925925</v>
       </c>
       <c r="E141">
         <v>69229</v>
@@ -23194,7 +23194,7 @@
         <v>46124.34533434028</v>
       </c>
       <c r="D142" s="1">
-        <v>46124.5953125</v>
+        <v>46124.3453125</v>
       </c>
       <c r="E142">
         <v>69322</v>
@@ -23337,7 +23337,7 @@
         <v>46124.34568268518</v>
       </c>
       <c r="D143" s="1">
-        <v>46124.595659722225</v>
+        <v>46124.345659722225</v>
       </c>
       <c r="E143">
         <v>69850</v>
@@ -23480,7 +23480,7 @@
         <v>46124.34605475694</v>
       </c>
       <c r="D144" s="1">
-        <v>46124.59599537037</v>
+        <v>46124.34599537037</v>
       </c>
       <c r="E144">
         <v>70274</v>
@@ -23623,7 +23623,7 @@
         <v>46124.34602800926</v>
       </c>
       <c r="D145" s="1">
-        <v>46124.59600694444</v>
+        <v>46124.34600694444</v>
       </c>
       <c r="E145">
         <v>70367</v>
@@ -23766,7 +23766,7 @@
         <v>46124.34637962963</v>
       </c>
       <c r="D146" s="1">
-        <v>46124.596354166664</v>
+        <v>46124.346354166664</v>
       </c>
       <c r="E146">
         <v>70947</v>
@@ -23909,7 +23909,7 @@
         <v>46124.346750578705</v>
       </c>
       <c r="D147" s="1">
-        <v>46124.59668981482</v>
+        <v>46124.34668981482</v>
       </c>
       <c r="E147">
         <v>71447</v>
@@ -24052,7 +24052,7 @@
         <v>46124.3467228125</v>
       </c>
       <c r="D148" s="1">
-        <v>46124.59670138889</v>
+        <v>46124.34670138889</v>
       </c>
       <c r="E148">
         <v>71548</v>
@@ -24195,7 +24195,7 @@
         <v>46124.347069780095</v>
       </c>
       <c r="D149" s="1">
-        <v>46124.59704861111</v>
+        <v>46124.34704861111</v>
       </c>
       <c r="E149">
         <v>72233</v>
@@ -24338,7 +24338,7 @@
         <v>46124.34744496528</v>
       </c>
       <c r="D150" s="1">
-        <v>46124.59738425926</v>
+        <v>46124.34738425926</v>
       </c>
       <c r="E150">
         <v>72744</v>
@@ -24481,7 +24481,7 @@
         <v>46124.34741863426</v>
       </c>
       <c r="D151" s="1">
-        <v>46124.597395833334</v>
+        <v>46124.347395833334</v>
       </c>
       <c r="E151">
         <v>72867</v>
@@ -24624,7 +24624,7 @@
         <v>46124.3477658912</v>
       </c>
       <c r="D152" s="1">
-        <v>46124.59774305556</v>
+        <v>46124.34774305556</v>
       </c>
       <c r="E152">
         <v>73470</v>
@@ -24767,7 +24767,7 @@
         <v>46124.348137650464</v>
       </c>
       <c r="D153" s="1">
-        <v>46124.598078703704</v>
+        <v>46124.348078703704</v>
       </c>
       <c r="E153">
         <v>73938</v>
@@ -24910,7 +24910,7 @@
         <v>46124.34811200231</v>
       </c>
       <c r="D154" s="1">
-        <v>46124.59809027778</v>
+        <v>46124.34809027778</v>
       </c>
       <c r="E154">
         <v>74034</v>
@@ -25053,7 +25053,7 @@
         <v>46124.34845981481</v>
       </c>
       <c r="D155" s="1">
-        <v>46124.5984375</v>
+        <v>46124.3484375</v>
       </c>
       <c r="E155">
         <v>74526</v>
@@ -25196,7 +25196,7 @@
         <v>46124.348831875</v>
       </c>
       <c r="D156" s="1">
-        <v>46124.59877314815</v>
+        <v>46124.34877314815</v>
       </c>
       <c r="E156">
         <v>74901</v>
@@ -25339,7 +25339,7 @@
         <v>46124.348806875</v>
       </c>
       <c r="D157" s="1">
-        <v>46124.59878472222</v>
+        <v>46124.34878472222</v>
       </c>
       <c r="E157">
         <v>74997</v>
@@ -25482,7 +25482,7 @@
         <v>46124.34915369213</v>
       </c>
       <c r="D158" s="1">
-        <v>46124.599131944444</v>
+        <v>46124.349131944444</v>
       </c>
       <c r="E158">
         <v>75476</v>
@@ -25625,7 +25625,7 @@
         <v>46124.34952631944</v>
       </c>
       <c r="D159" s="1">
-        <v>46124.59946759259</v>
+        <v>46124.34946759259</v>
       </c>
       <c r="E159">
         <v>75862</v>
@@ -25768,7 +25768,7 @@
         <v>46124.34950335648</v>
       </c>
       <c r="D160" s="1">
-        <v>46124.59947916667</v>
+        <v>46124.34947916667</v>
       </c>
       <c r="E160">
         <v>75954</v>
@@ -25911,7 +25911,7 @@
         <v>46124.34985025463</v>
       </c>
       <c r="D161" s="1">
-        <v>46124.59982638889</v>
+        <v>46124.34982638889</v>
       </c>
       <c r="E161">
         <v>76423</v>
@@ -26054,7 +26054,7 @@
         <v>46124.35019467593</v>
       </c>
       <c r="D162" s="1">
-        <v>46124.600173611114</v>
+        <v>46124.350173611114</v>
       </c>
       <c r="E162">
         <v>76916</v>
@@ -26197,7 +26197,7 @@
         <v>46124.35054265046</v>
       </c>
       <c r="D163" s="1">
-        <v>46124.60052083333</v>
+        <v>46124.35052083333</v>
       </c>
       <c r="E163">
         <v>77462</v>
@@ -26340,7 +26340,7 @@
         <v>46124.35091583333</v>
       </c>
       <c r="D164" s="1">
-        <v>46124.600856481484</v>
+        <v>46124.350856481484</v>
       </c>
       <c r="E164">
         <v>77928</v>
@@ -26483,7 +26483,7 @@
         <v>46124.350888912035</v>
       </c>
       <c r="D165" s="1">
-        <v>46124.60086805555</v>
+        <v>46124.35086805555</v>
       </c>
       <c r="E165">
         <v>78026</v>
@@ -26626,7 +26626,7 @@
         <v>46124.351236979164</v>
       </c>
       <c r="D166" s="1">
-        <v>46124.60121527778</v>
+        <v>46124.35121527778</v>
       </c>
       <c r="E166">
         <v>78619</v>
@@ -26769,7 +26769,7 @@
         <v>46124.351612025464</v>
       </c>
       <c r="D167" s="1">
-        <v>46124.60155092592</v>
+        <v>46124.35155092592</v>
       </c>
       <c r="E167">
         <v>79159</v>
@@ -26912,7 +26912,7 @@
         <v>46124.35158712963</v>
       </c>
       <c r="D168" s="1">
-        <v>46124.6015625</v>
+        <v>46124.3515625</v>
       </c>
       <c r="E168">
         <v>79264</v>
@@ -27055,7 +27055,7 @@
         <v>46124.35193221065</v>
       </c>
       <c r="D169" s="1">
-        <v>46124.60190972222</v>
+        <v>46124.35190972222</v>
       </c>
       <c r="E169">
         <v>79870</v>
@@ -27198,7 +27198,7 @@
         <v>46124.35230443287</v>
       </c>
       <c r="D170" s="1">
-        <v>46124.60224537037</v>
+        <v>46124.35224537037</v>
       </c>
       <c r="E170">
         <v>80318</v>
@@ -27341,7 +27341,7 @@
         <v>46124.35228219908</v>
       </c>
       <c r="D171" s="1">
-        <v>46124.60225694445</v>
+        <v>46124.35225694445</v>
       </c>
       <c r="E171">
         <v>80414</v>
@@ -27484,7 +27484,7 @@
         <v>46124.35262672454</v>
       </c>
       <c r="D172" s="1">
-        <v>46124.60260416667</v>
+        <v>46124.35260416667</v>
       </c>
       <c r="E172">
         <v>80905</v>
@@ -27627,7 +27627,7 @@
         <v>46124.3530002662</v>
       </c>
       <c r="D173" s="1">
-        <v>46124.60293981482</v>
+        <v>46124.35293981482</v>
       </c>
       <c r="E173">
         <v>81268</v>
@@ -27770,7 +27770,7 @@
         <v>46124.35297269676</v>
       </c>
       <c r="D174" s="1">
-        <v>46124.602951388886</v>
+        <v>46124.352951388886</v>
       </c>
       <c r="E174">
         <v>81368</v>
@@ -27913,7 +27913,7 @@
         <v>46124.35332152778</v>
       </c>
       <c r="D175" s="1">
-        <v>46124.60329861111</v>
+        <v>46124.35329861111</v>
       </c>
       <c r="E175">
         <v>81815</v>
@@ -28056,7 +28056,7 @@
         <v>46124.35369435185</v>
       </c>
       <c r="D176" s="1">
-        <v>46124.603634259256</v>
+        <v>46124.353634259256</v>
       </c>
       <c r="E176">
         <v>82216</v>
@@ -28199,7 +28199,7 @@
         <v>46124.35366850694</v>
       </c>
       <c r="D177" s="1">
-        <v>46124.60364583333</v>
+        <v>46124.35364583333</v>
       </c>
       <c r="E177">
         <v>82313</v>
@@ -28342,7 +28342,7 @@
         <v>46124.354014247685</v>
       </c>
       <c r="D178" s="1">
-        <v>46124.603993055556</v>
+        <v>46124.353993055556</v>
       </c>
       <c r="E178">
         <v>82834</v>
@@ -28485,7 +28485,7 @@
         <v>46124.35436440972</v>
       </c>
       <c r="D179" s="1">
-        <v>46124.60434027778</v>
+        <v>46124.35434027778</v>
       </c>
       <c r="E179">
         <v>83412</v>
@@ -28628,7 +28628,7 @@
         <v>46124.35471104167</v>
       </c>
       <c r="D180" s="1">
-        <v>46124.6046875</v>
+        <v>46124.3546875</v>
       </c>
       <c r="E180">
         <v>84001</v>
@@ -28771,7 +28771,7 @@
         <v>46124.35508231482</v>
       </c>
       <c r="D181" s="1">
-        <v>46124.60502314815</v>
+        <v>46124.35502314815</v>
       </c>
       <c r="E181">
         <v>84475</v>
@@ -28914,7 +28914,7 @@
         <v>46124.355056030094</v>
       </c>
       <c r="D182" s="1">
-        <v>46124.60503472222</v>
+        <v>46124.35503472222</v>
       </c>
       <c r="E182">
         <v>84573</v>
@@ -29057,7 +29057,7 @@
         <v>46124.35540569444</v>
       </c>
       <c r="D183" s="1">
-        <v>46124.60538194444</v>
+        <v>46124.35538194444</v>
       </c>
       <c r="E183">
         <v>85120</v>
@@ -29200,7 +29200,7 @@
         <v>46124.35577747685</v>
       </c>
       <c r="D184" s="1">
-        <v>46124.605717592596</v>
+        <v>46124.355717592596</v>
       </c>
       <c r="E184">
         <v>85499</v>
@@ -29343,7 +29343,7 @@
         <v>46124.355757337966</v>
       </c>
       <c r="D185" s="1">
-        <v>46124.605717592596</v>
+        <v>46124.355717592596</v>
       </c>
       <c r="E185">
         <v>85500</v>
@@ -29465,7 +29465,7 @@
         <v>46124.35575101852</v>
       </c>
       <c r="D186" s="1">
-        <v>46124.605729166666</v>
+        <v>46124.355729166666</v>
       </c>
       <c r="E186">
         <v>85599</v>
@@ -29608,7 +29608,7 @@
         <v>46124.35609905093</v>
       </c>
       <c r="D187" s="1">
-        <v>46124.60607638889</v>
+        <v>46124.35607638889</v>
       </c>
       <c r="E187">
         <v>86041</v>
@@ -29751,7 +29751,7 @@
         <v>46124.35647144676</v>
       </c>
       <c r="D188" s="1">
-        <v>46124.606412037036</v>
+        <v>46124.356412037036</v>
       </c>
       <c r="E188">
         <v>86328</v>
@@ -29894,7 +29894,7 @@
         <v>46124.35644456019</v>
       </c>
       <c r="D189" s="1">
-        <v>46124.60642361111</v>
+        <v>46124.35642361111</v>
       </c>
       <c r="E189">
         <v>86428</v>
@@ -30037,7 +30037,7 @@
         <v>46124.356792280094</v>
       </c>
       <c r="D190" s="1">
-        <v>46124.606770833336</v>
+        <v>46124.356770833336</v>
       </c>
       <c r="E190">
         <v>86851</v>
@@ -30180,7 +30180,7 @@
         <v>46124.35716623843</v>
       </c>
       <c r="D191" s="1">
-        <v>46124.60710648148</v>
+        <v>46124.35710648148</v>
       </c>
       <c r="E191">
         <v>87218</v>
@@ -30323,7 +30323,7 @@
         <v>46124.35714054398</v>
       </c>
       <c r="D192" s="1">
-        <v>46124.60711805556</v>
+        <v>46124.35711805556</v>
       </c>
       <c r="E192">
         <v>87318</v>
@@ -30466,7 +30466,7 @@
         <v>46124.35748673611</v>
       </c>
       <c r="D193" s="1">
-        <v>46124.607465277775</v>
+        <v>46124.357465277775</v>
       </c>
       <c r="E193">
         <v>87819</v>
@@ -30609,7 +30609,7 @@
         <v>46124.35786153935</v>
       </c>
       <c r="D194" s="1">
-        <v>46124.60780092593</v>
+        <v>46124.35780092593</v>
       </c>
       <c r="E194">
         <v>88257</v>
@@ -30752,7 +30752,7 @@
         <v>46124.357833622686</v>
       </c>
       <c r="D195" s="1">
-        <v>46124.6078125</v>
+        <v>46124.3578125</v>
       </c>
       <c r="E195">
         <v>88357</v>
@@ -30895,7 +30895,7 @@
         <v>46124.35818145833</v>
       </c>
       <c r="D196" s="1">
-        <v>46124.60815972222</v>
+        <v>46124.35815972222</v>
       </c>
       <c r="E196">
         <v>88932</v>
@@ -31038,7 +31038,7 @@
         <v>46124.358555520834</v>
       </c>
       <c r="D197" s="1">
-        <v>46124.60849537037</v>
+        <v>46124.35849537037</v>
       </c>
       <c r="E197">
         <v>89349</v>
@@ -31181,7 +31181,7 @@
         <v>46124.35853633102</v>
       </c>
       <c r="D198" s="1">
-        <v>46124.60849537037</v>
+        <v>46124.35849537037</v>
       </c>
       <c r="E198">
         <v>89348</v>
@@ -31303,7 +31303,7 @@
         <v>46124.35852952546</v>
       </c>
       <c r="D199" s="1">
-        <v>46124.608506944445</v>
+        <v>46124.358506944445</v>
       </c>
       <c r="E199">
         <v>89448</v>
@@ -31446,7 +31446,7 @@
         <v>46124.35887609953</v>
       </c>
       <c r="D200" s="1">
-        <v>46124.60885416667</v>
+        <v>46124.35885416667</v>
       </c>
       <c r="E200">
         <v>89912</v>
@@ -31589,7 +31589,7 @@
         <v>46124.35925018518</v>
       </c>
       <c r="D201" s="1">
-        <v>46124.609189814815</v>
+        <v>46124.359189814815</v>
       </c>
       <c r="E201">
         <v>90254</v>
@@ -31732,7 +31732,7 @@
         <v>46124.35922604167</v>
       </c>
       <c r="D202" s="1">
-        <v>46124.60920138889</v>
+        <v>46124.35920138889</v>
       </c>
       <c r="E202">
         <v>90350</v>
@@ -31875,7 +31875,7 @@
         <v>46124.359570127315</v>
       </c>
       <c r="D203" s="1">
-        <v>46124.60954861111</v>
+        <v>46124.35954861111</v>
       </c>
       <c r="E203">
         <v>90708</v>
@@ -32018,7 +32018,7 @@
         <v>46124.359943055555</v>
       </c>
       <c r="D204" s="1">
-        <v>46124.60988425926</v>
+        <v>46124.35988425926</v>
       </c>
       <c r="E204">
         <v>90958</v>
@@ -32161,7 +32161,7 @@
         <v>46124.359917361115</v>
       </c>
       <c r="D205" s="1">
-        <v>46124.60989583333</v>
+        <v>46124.35989583333</v>
       </c>
       <c r="E205">
         <v>91052</v>
@@ -32304,7 +32304,7 @@
         <v>46124.36026550926</v>
       </c>
       <c r="D206" s="1">
-        <v>46124.610243055555</v>
+        <v>46124.360243055555</v>
       </c>
       <c r="E206">
         <v>91446</v>
@@ -32447,7 +32447,7 @@
         <v>46124.36064328704</v>
       </c>
       <c r="D207" s="1">
-        <v>46124.6105787037</v>
+        <v>46124.3605787037</v>
       </c>
       <c r="E207">
         <v>91784</v>
@@ -32590,7 +32590,7 @@
         <v>46124.36061138889</v>
       </c>
       <c r="D208" s="1">
-        <v>46124.61059027778</v>
+        <v>46124.36059027778</v>
       </c>
       <c r="E208">
         <v>91884</v>
@@ -32733,7 +32733,7 @@
         <v>46124.36096179398</v>
       </c>
       <c r="D209" s="1">
-        <v>46124.6109375</v>
+        <v>46124.3609375</v>
       </c>
       <c r="E209">
         <v>92368</v>
@@ -32876,7 +32876,7 @@
         <v>46124.36133607639</v>
       </c>
       <c r="D210" s="1">
-        <v>46124.61127314815</v>
+        <v>46124.36127314815</v>
       </c>
       <c r="E210">
         <v>92770</v>
@@ -33019,7 +33019,7 @@
         <v>46124.3613062963</v>
       </c>
       <c r="D211" s="1">
-        <v>46124.611284722225</v>
+        <v>46124.361284722225</v>
       </c>
       <c r="E211">
         <v>92868</v>
@@ -33162,7 +33162,7 @@
         <v>46124.36165348379</v>
       </c>
       <c r="D212" s="1">
-        <v>46124.61163194444</v>
+        <v>46124.36163194444</v>
       </c>
       <c r="E212">
         <v>93371</v>
@@ -33305,7 +33305,7 @@
         <v>46124.36202707176</v>
       </c>
       <c r="D213" s="1">
-        <v>46124.611967592595</v>
+        <v>46124.361967592595</v>
       </c>
       <c r="E213">
         <v>93781</v>
@@ -33448,7 +33448,7 @@
         <v>46124.36200064815</v>
       </c>
       <c r="D214" s="1">
-        <v>46124.611979166664</v>
+        <v>46124.361979166664</v>
       </c>
       <c r="E214">
         <v>93881</v>
@@ -33591,7 +33591,7 @@
         <v>46124.362352511576</v>
       </c>
       <c r="D215" s="1">
-        <v>46124.61232638889</v>
+        <v>46124.36232638889</v>
       </c>
       <c r="E215">
         <v>94357</v>
@@ -33734,7 +33734,7 @@
         <v>46124.36272211806</v>
       </c>
       <c r="D216" s="1">
-        <v>46124.612662037034</v>
+        <v>46124.362662037034</v>
       </c>
       <c r="E216">
         <v>94709</v>
@@ -33877,7 +33877,7 @@
         <v>46124.36269570602</v>
       </c>
       <c r="D217" s="1">
-        <v>46124.61267361111</v>
+        <v>46124.36267361111</v>
       </c>
       <c r="E217">
         <v>94809</v>
@@ -34020,7 +34020,7 @@
         <v>46124.36304403935</v>
       </c>
       <c r="D218" s="1">
-        <v>46124.613020833334</v>
+        <v>46124.363020833334</v>
       </c>
       <c r="E218">
         <v>95212</v>
@@ -34163,7 +34163,7 @@
         <v>46124.36341675926</v>
       </c>
       <c r="D219" s="1">
-        <v>46124.61335648148</v>
+        <v>46124.36335648148</v>
       </c>
       <c r="E219">
         <v>95506</v>
@@ -34306,7 +34306,7 @@
         <v>46124.363392025465</v>
       </c>
       <c r="D220" s="1">
-        <v>46124.61336805556</v>
+        <v>46124.36336805556</v>
       </c>
       <c r="E220">
         <v>95605</v>
@@ -34449,7 +34449,7 @@
         <v>46124.36373648148</v>
       </c>
       <c r="D221" s="1">
-        <v>46124.61371527778</v>
+        <v>46124.36371527778</v>
       </c>
       <c r="E221">
         <v>96004</v>
@@ -34592,7 +34592,7 @@
         <v>46124.36411292824</v>
       </c>
       <c r="D222" s="1">
-        <v>46124.61405092593</v>
+        <v>46124.36405092593</v>
       </c>
       <c r="E222">
         <v>96350</v>
@@ -34735,7 +34735,7 @@
         <v>46124.36408694444</v>
       </c>
       <c r="D223" s="1">
-        <v>46124.6140625</v>
+        <v>46124.3640625</v>
       </c>
       <c r="E223">
         <v>96449</v>
@@ -34878,7 +34878,7 @@
         <v>46124.364433807874</v>
       </c>
       <c r="D224" s="1">
-        <v>46124.61440972222</v>
+        <v>46124.36440972222</v>
       </c>
       <c r="E224">
         <v>96908</v>
@@ -35021,7 +35021,7 @@
         <v>46124.36480607639</v>
       </c>
       <c r="D225" s="1">
-        <v>46124.61474537037</v>
+        <v>46124.36474537037</v>
       </c>
       <c r="E225">
         <v>97273</v>
@@ -35164,7 +35164,7 @@
         <v>46124.36477832176</v>
       </c>
       <c r="D226" s="1">
-        <v>46124.614756944444</v>
+        <v>46124.364756944444</v>
       </c>
       <c r="E226">
         <v>97372</v>
@@ -35307,7 +35307,7 @@
         <v>46124.36513748843</v>
       </c>
       <c r="D227" s="1">
-        <v>46124.61509259259</v>
+        <v>46124.36509259259</v>
       </c>
       <c r="E227">
         <v>97731</v>
@@ -35450,7 +35450,7 @@
         <v>46124.36512707176</v>
       </c>
       <c r="D228" s="1">
-        <v>46124.61510416667</v>
+        <v>46124.36510416667</v>
       </c>
       <c r="E228">
         <v>97831</v>
@@ -35593,7 +35593,7 @@
         <v>46124.36550011574</v>
       </c>
       <c r="D229" s="1">
-        <v>46124.615439814814</v>
+        <v>46124.365439814814</v>
       </c>
       <c r="E229">
         <v>98147</v>
@@ -35736,7 +35736,7 @@
         <v>46124.36547665509</v>
       </c>
       <c r="D230" s="1">
-        <v>46124.61545138889</v>
+        <v>46124.36545138889</v>
       </c>
       <c r="E230">
         <v>98241</v>
@@ -35879,7 +35879,7 @@
         <v>46124.365822569445</v>
       </c>
       <c r="D231" s="1">
-        <v>46124.615798611114</v>
+        <v>46124.365798611114</v>
       </c>
       <c r="E231">
         <v>98649</v>
@@ -36022,7 +36022,7 @@
         <v>46124.36619417824</v>
       </c>
       <c r="D232" s="1">
-        <v>46124.61613425926</v>
+        <v>46124.36613425926</v>
       </c>
       <c r="E232">
         <v>98964</v>
@@ -36165,7 +36165,7 @@
         <v>46124.366168229164</v>
       </c>
       <c r="D233" s="1">
-        <v>46124.61614583333</v>
+        <v>46124.36614583333</v>
       </c>
       <c r="E233">
         <v>99059</v>
@@ -36464,7 +36464,7 @@
         <v>46124.366785798615</v>
       </c>
       <c r="D2" s="1">
-        <v>46124.61649305555</v>
+        <v>46124.36649305555</v>
       </c>
       <c r="E2">
         <v>96269</v>
@@ -36571,7 +36571,7 @@
         <v>46124.36685989583</v>
       </c>
       <c r="D3" s="1">
-        <v>46124.61682870371</v>
+        <v>46124.36682870371</v>
       </c>
       <c r="E3">
         <v>91767</v>
@@ -36681,7 +36681,7 @@
         <v>46124.36686287037</v>
       </c>
       <c r="D4" s="1">
-        <v>46124.61684027778</v>
+        <v>46124.36684027778</v>
       </c>
       <c r="E4">
         <v>91530</v>
@@ -36824,7 +36824,7 @@
         <v>46124.36720699074</v>
       </c>
       <c r="D5" s="1">
-        <v>46124.61717592592</v>
+        <v>46124.36717592592</v>
       </c>
       <c r="E5">
         <v>87514</v>
@@ -36946,7 +36946,7 @@
         <v>46124.36721309028</v>
       </c>
       <c r="D6" s="1">
-        <v>46124.6171875</v>
+        <v>46124.3671875</v>
       </c>
       <c r="E6">
         <v>87315</v>
@@ -37089,7 +37089,7 @@
         <v>46124.36755675926</v>
       </c>
       <c r="D7" s="1">
-        <v>46124.61752314815</v>
+        <v>46124.36752314815</v>
       </c>
       <c r="E7">
         <v>83665</v>
@@ -37211,7 +37211,7 @@
         <v>46124.36755679398</v>
       </c>
       <c r="D8" s="1">
-        <v>46124.61753472222</v>
+        <v>46124.36753472222</v>
       </c>
       <c r="E8">
         <v>83487</v>
@@ -37354,7 +37354,7 @@
         <v>46124.36790064815</v>
       </c>
       <c r="D9" s="1">
-        <v>46124.61787037037</v>
+        <v>46124.36787037037</v>
       </c>
       <c r="E9">
         <v>80092</v>
@@ -37476,7 +37476,7 @@
         <v>46124.367903032406</v>
       </c>
       <c r="D10" s="1">
-        <v>46124.61788194445</v>
+        <v>46124.36788194445</v>
       </c>
       <c r="E10">
         <v>79918</v>
@@ -37619,7 +37619,7 @@
         <v>46124.36824762732</v>
       </c>
       <c r="D11" s="1">
-        <v>46124.61821759259</v>
+        <v>46124.36821759259</v>
       </c>
       <c r="E11">
         <v>76883</v>
@@ -37741,7 +37741,7 @@
         <v>46124.368254479166</v>
       </c>
       <c r="D12" s="1">
-        <v>46124.61822916667</v>
+        <v>46124.36822916667</v>
       </c>
       <c r="E12">
         <v>76728</v>
@@ -37884,7 +37884,7 @@
         <v>46124.36859386574</v>
       </c>
       <c r="D13" s="1">
-        <v>46124.61856481482</v>
+        <v>46124.36856481482</v>
       </c>
       <c r="E13">
         <v>73910</v>
@@ -38006,7 +38006,7 @@
         <v>46124.368598043984</v>
       </c>
       <c r="D14" s="1">
-        <v>46124.618576388886</v>
+        <v>46124.368576388886</v>
       </c>
       <c r="E14">
         <v>73775</v>
@@ -38149,7 +38149,7 @@
         <v>46124.3689421875</v>
       </c>
       <c r="D15" s="1">
-        <v>46124.61891203704</v>
+        <v>46124.36891203704</v>
       </c>
       <c r="E15">
         <v>71298</v>
@@ -38271,7 +38271,7 @@
         <v>46124.36894552084</v>
       </c>
       <c r="D16" s="1">
-        <v>46124.61892361111</v>
+        <v>46124.36892361111</v>
       </c>
       <c r="E16">
         <v>71200</v>
@@ -38414,7 +38414,7 @@
         <v>46124.36928712963</v>
       </c>
       <c r="D17" s="1">
-        <v>46124.619259259256</v>
+        <v>46124.369259259256</v>
       </c>
       <c r="E17">
         <v>68762</v>
@@ -38536,7 +38536,7 @@
         <v>46124.36929466435</v>
       </c>
       <c r="D18" s="1">
-        <v>46124.61927083333</v>
+        <v>46124.36927083333</v>
       </c>
       <c r="E18">
         <v>68644</v>
@@ -38679,7 +38679,7 @@
         <v>46124.36963537037</v>
       </c>
       <c r="D19" s="1">
-        <v>46124.61960648148</v>
+        <v>46124.36960648148</v>
       </c>
       <c r="E19">
         <v>66475</v>
@@ -38801,7 +38801,7 @@
         <v>46124.369640046294</v>
       </c>
       <c r="D20" s="1">
-        <v>46124.619618055556</v>
+        <v>46124.369618055556</v>
       </c>
       <c r="E20">
         <v>66409</v>
@@ -38944,7 +38944,7 @@
         <v>46124.36998474537</v>
       </c>
       <c r="D21" s="1">
-        <v>46124.6199537037</v>
+        <v>46124.3699537037</v>
       </c>
       <c r="E21">
         <v>64309</v>
@@ -39066,7 +39066,7 @@
         <v>46124.36998643519</v>
       </c>
       <c r="D22" s="1">
-        <v>46124.61996527778</v>
+        <v>46124.36996527778</v>
       </c>
       <c r="E22">
         <v>64238</v>
@@ -39209,7 +39209,7 @@
         <v>46124.37033</v>
       </c>
       <c r="D23" s="1">
-        <v>46124.620300925926</v>
+        <v>46124.370300925926</v>
       </c>
       <c r="E23">
         <v>62111</v>
@@ -39331,7 +39331,7 @@
         <v>46124.37033443287</v>
       </c>
       <c r="D24" s="1">
-        <v>46124.6203125</v>
+        <v>46124.3703125</v>
       </c>
       <c r="E24">
         <v>62033</v>
@@ -39474,7 +39474,7 @@
         <v>46124.37067675926</v>
       </c>
       <c r="D25" s="1">
-        <v>46124.62064814815</v>
+        <v>46124.37064814815</v>
       </c>
       <c r="E25">
         <v>60080</v>
@@ -39596,7 +39596,7 @@
         <v>46124.370682581015</v>
       </c>
       <c r="D26" s="1">
-        <v>46124.62065972222</v>
+        <v>46124.37065972222</v>
       </c>
       <c r="E26">
         <v>59995</v>
@@ -39739,7 +39739,7 @@
         <v>46124.37102684028</v>
       </c>
       <c r="D27" s="1">
-        <v>46124.62099537037</v>
+        <v>46124.37099537037</v>
       </c>
       <c r="E27">
         <v>58229</v>
@@ -39861,7 +39861,7 @@
         <v>46124.37102871528</v>
       </c>
       <c r="D28" s="1">
-        <v>46124.62100694444</v>
+        <v>46124.37100694444</v>
       </c>
       <c r="E28">
         <v>58179</v>
@@ -40004,7 +40004,7 @@
         <v>46124.3713896412</v>
       </c>
       <c r="D29" s="1">
-        <v>46124.621342592596</v>
+        <v>46124.371342592596</v>
       </c>
       <c r="E29">
         <v>56529</v>
@@ -40126,7 +40126,7 @@
         <v>46124.371381516205</v>
       </c>
       <c r="D30" s="1">
-        <v>46124.621354166666</v>
+        <v>46124.371354166666</v>
       </c>
       <c r="E30">
         <v>56490</v>
@@ -40269,7 +40269,7 @@
         <v>46124.37171979166</v>
       </c>
       <c r="D31" s="1">
-        <v>46124.62168981481</v>
+        <v>46124.37168981481</v>
       </c>
       <c r="E31">
         <v>54915</v>
@@ -40391,7 +40391,7 @@
         <v>46124.37172350694</v>
       </c>
       <c r="D32" s="1">
-        <v>46124.62170138889</v>
+        <v>46124.37170138889</v>
       </c>
       <c r="E32">
         <v>54872</v>
@@ -40534,7 +40534,7 @@
         <v>46124.372073287035</v>
       </c>
       <c r="D33" s="1">
-        <v>46124.622037037036</v>
+        <v>46124.372037037036</v>
       </c>
       <c r="E33">
         <v>53363</v>
@@ -40656,7 +40656,7 @@
         <v>46124.3720703125</v>
       </c>
       <c r="D34" s="1">
-        <v>46124.62204861111</v>
+        <v>46124.37204861111</v>
       </c>
       <c r="E34">
         <v>53337</v>
@@ -40799,7 +40799,7 @@
         <v>46124.372413715275</v>
       </c>
       <c r="D35" s="1">
-        <v>46124.62238425926</v>
+        <v>46124.37238425926</v>
       </c>
       <c r="E35">
         <v>51834</v>
@@ -40921,7 +40921,7 @@
         <v>46124.37241780093</v>
       </c>
       <c r="D36" s="1">
-        <v>46124.622395833336</v>
+        <v>46124.372395833336</v>
       </c>
       <c r="E36">
         <v>51810</v>
@@ -41064,7 +41064,7 @@
         <v>46124.37275994213</v>
       </c>
       <c r="D37" s="1">
-        <v>46124.62273148148</v>
+        <v>46124.37273148148</v>
       </c>
       <c r="E37">
         <v>50302</v>
@@ -41186,7 +41186,7 @@
         <v>46124.373108900465</v>
       </c>
       <c r="D38" s="1">
-        <v>46124.623078703706</v>
+        <v>46124.373078703706</v>
       </c>
       <c r="E38">
         <v>48792</v>
@@ -41308,7 +41308,7 @@
         <v>46124.37311331018</v>
       </c>
       <c r="D39" s="1">
-        <v>46124.623090277775</v>
+        <v>46124.373090277775</v>
       </c>
       <c r="E39">
         <v>48770</v>
@@ -41451,7 +41451,7 @@
         <v>46124.37345488426</v>
       </c>
       <c r="D40" s="1">
-        <v>46124.62342592593</v>
+        <v>46124.37342592593</v>
       </c>
       <c r="E40">
         <v>47411</v>
@@ -41573,7 +41573,7 @@
         <v>46124.37346008102</v>
       </c>
       <c r="D41" s="1">
-        <v>46124.6234375</v>
+        <v>46124.3734375</v>
       </c>
       <c r="E41">
         <v>47390</v>
@@ -41716,7 +41716,7 @@
         <v>46124.37380168981</v>
       </c>
       <c r="D42" s="1">
-        <v>46124.623773148145</v>
+        <v>46124.373773148145</v>
       </c>
       <c r="E42">
         <v>46095</v>
@@ -41838,7 +41838,7 @@
         <v>46124.37380716435</v>
       </c>
       <c r="D43" s="1">
-        <v>46124.62378472222</v>
+        <v>46124.37378472222</v>
       </c>
       <c r="E43">
         <v>46070</v>
@@ -41981,7 +41981,7 @@
         <v>46124.374157175924</v>
       </c>
       <c r="D44" s="1">
-        <v>46124.62412037037</v>
+        <v>46124.37412037037</v>
       </c>
       <c r="E44">
         <v>44691</v>
@@ -42103,7 +42103,7 @@
         <v>46124.3741575463</v>
       </c>
       <c r="D45" s="1">
-        <v>46124.624131944445</v>
+        <v>46124.374131944445</v>
       </c>
       <c r="E45">
         <v>44654</v>
@@ -42246,7 +42246,7 @@
         <v>46124.374505555556</v>
       </c>
       <c r="D46" s="1">
-        <v>46124.62446759259</v>
+        <v>46124.37446759259</v>
       </c>
       <c r="E46">
         <v>43358</v>
@@ -42368,7 +42368,7 @@
         <v>46124.37450068287</v>
       </c>
       <c r="D47" s="1">
-        <v>46124.62447916667</v>
+        <v>46124.37447916667</v>
       </c>
       <c r="E47">
         <v>43325</v>
@@ -42511,7 +42511,7 @@
         <v>46124.37484511574</v>
       </c>
       <c r="D48" s="1">
-        <v>46124.624814814815</v>
+        <v>46124.374814814815</v>
       </c>
       <c r="E48">
         <v>42095</v>
@@ -42633,7 +42633,7 @@
         <v>46124.37484863426</v>
       </c>
       <c r="D49" s="1">
-        <v>46124.62482638889</v>
+        <v>46124.37482638889</v>
       </c>
       <c r="E49">
         <v>42065</v>
@@ -42776,7 +42776,7 @@
         <v>46124.37519305556</v>
       </c>
       <c r="D50" s="1">
-        <v>46124.62516203704</v>
+        <v>46124.37516203704</v>
       </c>
       <c r="E50">
         <v>40930</v>
@@ -42898,7 +42898,7 @@
         <v>46124.375539050925</v>
       </c>
       <c r="D51" s="1">
-        <v>46124.62550925926</v>
+        <v>46124.37550925926</v>
       </c>
       <c r="E51">
         <v>39844</v>
@@ -43020,7 +43020,7 @@
         <v>46124.37625439815</v>
       </c>
       <c r="D52" s="1">
-        <v>46124.6262037037</v>
+        <v>46124.3762037037</v>
       </c>
       <c r="E52">
         <v>37600</v>
@@ -43142,7 +43142,7 @@
         <v>46124.37623692129</v>
       </c>
       <c r="D53" s="1">
-        <v>46124.62621527778</v>
+        <v>46124.37621527778</v>
       </c>
       <c r="E53">
         <v>37606</v>
@@ -43285,7 +43285,7 @@
         <v>46124.37658440972</v>
       </c>
       <c r="D54" s="1">
-        <v>46124.6265625</v>
+        <v>46124.3765625</v>
       </c>
       <c r="E54">
         <v>36507</v>
@@ -43428,7 +43428,7 @@
         <v>46124.37692678241</v>
       </c>
       <c r="D55" s="1">
-        <v>46124.62689814815</v>
+        <v>46124.37689814815</v>
       </c>
       <c r="E55">
         <v>35392</v>
@@ -43550,7 +43550,7 @@
         <v>46124.37729563657</v>
       </c>
       <c r="D56" s="1">
-        <v>46124.62724537037</v>
+        <v>46124.37724537037</v>
       </c>
       <c r="E56">
         <v>34322</v>
@@ -43672,7 +43672,7 @@
         <v>46124.37728361111</v>
       </c>
       <c r="D57" s="1">
-        <v>46124.62725694444</v>
+        <v>46124.37725694444</v>
       </c>
       <c r="E57">
         <v>34308</v>
@@ -43815,7 +43815,7 @@
         <v>46124.37763125</v>
       </c>
       <c r="D58" s="1">
-        <v>46124.627592592595</v>
+        <v>46124.377592592595</v>
       </c>
       <c r="E58">
         <v>33331</v>
@@ -43937,7 +43937,7 @@
         <v>46124.37801328704</v>
       </c>
       <c r="D59" s="1">
-        <v>46124.62793981482</v>
+        <v>46124.37793981482</v>
       </c>
       <c r="E59">
         <v>32358</v>
@@ -44080,7 +44080,7 @@
         <v>46124.37797072917</v>
       </c>
       <c r="D60" s="1">
-        <v>46124.62793981482</v>
+        <v>46124.37793981482</v>
       </c>
       <c r="E60">
         <v>32402</v>
@@ -44202,7 +44202,7 @@
         <v>46124.378318993055</v>
       </c>
       <c r="D61" s="1">
-        <v>46124.628287037034</v>
+        <v>46124.378287037034</v>
       </c>
       <c r="E61">
         <v>31441</v>
@@ -44324,7 +44324,7 @@
         <v>46124.37832710648</v>
       </c>
       <c r="D62" s="1">
-        <v>46124.62829861111</v>
+        <v>46124.37829861111</v>
       </c>
       <c r="E62">
         <v>31448</v>
@@ -44467,7 +44467,7 @@
         <v>46124.378663668984</v>
       </c>
       <c r="D63" s="1">
-        <v>46124.62863425926</v>
+        <v>46124.37863425926</v>
       </c>
       <c r="E63">
         <v>30519</v>
@@ -44589,7 +44589,7 @@
         <v>46124.37867362268</v>
       </c>
       <c r="D64" s="1">
-        <v>46124.628645833334</v>
+        <v>46124.378645833334</v>
       </c>
       <c r="E64">
         <v>30532</v>
@@ -44732,7 +44732,7 @@
         <v>46124.37936247685</v>
       </c>
       <c r="D65" s="1">
-        <v>46124.62934027778</v>
+        <v>46124.37934027778</v>
       </c>
       <c r="E65">
         <v>28615</v>
@@ -44875,7 +44875,7 @@
         <v>46124.37970618055</v>
       </c>
       <c r="D66" s="1">
-        <v>46124.62967592593</v>
+        <v>46124.37967592593</v>
       </c>
       <c r="E66">
         <v>27697</v>
@@ -44997,7 +44997,7 @@
         <v>46124.37971011574</v>
       </c>
       <c r="D67" s="1">
-        <v>46124.6296875</v>
+        <v>46124.3796875</v>
       </c>
       <c r="E67">
         <v>27714</v>
@@ -45140,7 +45140,7 @@
         <v>46124.38005357639</v>
       </c>
       <c r="D68" s="1">
-        <v>46124.63002314815</v>
+        <v>46124.38002314815</v>
       </c>
       <c r="E68">
         <v>26831</v>
@@ -45262,7 +45262,7 @@
         <v>46124.38006306713</v>
       </c>
       <c r="D69" s="1">
-        <v>46124.63003472222</v>
+        <v>46124.38003472222</v>
       </c>
       <c r="E69">
         <v>26851</v>
@@ -45405,7 +45405,7 @@
         <v>46124.38039857639</v>
       </c>
       <c r="D70" s="1">
-        <v>46124.63037037037</v>
+        <v>46124.38037037037</v>
       </c>
       <c r="E70">
         <v>26014</v>
@@ -45527,7 +45527,7 @@
         <v>46124.380404351854</v>
       </c>
       <c r="D71" s="1">
-        <v>46124.630381944444</v>
+        <v>46124.380381944444</v>
       </c>
       <c r="E71">
         <v>26038</v>
@@ -45670,7 +45670,7 @@
         <v>46124.3807509375</v>
       </c>
       <c r="D72" s="1">
-        <v>46124.63072916667</v>
+        <v>46124.38072916667</v>
       </c>
       <c r="E72">
         <v>25218</v>
@@ -45813,7 +45813,7 @@
         <v>46124.38109378472</v>
       </c>
       <c r="D73" s="1">
-        <v>46124.631064814814</v>
+        <v>46124.381064814814</v>
       </c>
       <c r="E73">
         <v>24409</v>
@@ -45935,7 +45935,7 @@
         <v>46124.381097847225</v>
       </c>
       <c r="D74" s="1">
-        <v>46124.63107638889</v>
+        <v>46124.38107638889</v>
       </c>
       <c r="E74">
         <v>24429</v>
@@ -46078,7 +46078,7 @@
         <v>46124.381446631945</v>
       </c>
       <c r="D75" s="1">
-        <v>46124.631423611114</v>
+        <v>46124.381423611114</v>
       </c>
       <c r="E75">
         <v>23642</v>
@@ -46221,7 +46221,7 @@
         <v>46124.381789618055</v>
       </c>
       <c r="D76" s="1">
-        <v>46124.63175925926</v>
+        <v>46124.38175925926</v>
       </c>
       <c r="E76">
         <v>22831</v>
@@ -46343,7 +46343,7 @@
         <v>46124.38179179398</v>
       </c>
       <c r="D77" s="1">
-        <v>46124.63177083333</v>
+        <v>46124.38177083333</v>
       </c>
       <c r="E77">
         <v>22859</v>
@@ -46486,7 +46486,7 @@
         <v>46124.38213412037</v>
       </c>
       <c r="D78" s="1">
-        <v>46124.632106481484</v>
+        <v>46124.382106481484</v>
       </c>
       <c r="E78">
         <v>22037</v>
@@ -46608,7 +46608,7 @@
         <v>46124.382490902775</v>
       </c>
       <c r="D79" s="1">
-        <v>46124.63246527778</v>
+        <v>46124.38246527778</v>
       </c>
       <c r="E79">
         <v>21291</v>
@@ -46751,7 +46751,7 @@
         <v>46124.382832662035</v>
       </c>
       <c r="D80" s="1">
-        <v>46124.63280092592</v>
+        <v>46124.38280092592</v>
       </c>
       <c r="E80">
         <v>20459</v>
@@ -46873,7 +46873,7 @@
         <v>46124.3828346875</v>
       </c>
       <c r="D81" s="1">
-        <v>46124.6328125</v>
+        <v>46124.3828125</v>
       </c>
       <c r="E81">
         <v>20482</v>
@@ -47016,7 +47016,7 @@
         <v>46124.38317934028</v>
       </c>
       <c r="D82" s="1">
-        <v>46124.63314814815</v>
+        <v>46124.38314814815</v>
       </c>
       <c r="E82">
         <v>19688</v>
@@ -47138,7 +47138,7 @@
         <v>46124.38318134259</v>
       </c>
       <c r="D83" s="1">
-        <v>46124.63315972222</v>
+        <v>46124.38315972222</v>
       </c>
       <c r="E83">
         <v>19707</v>
@@ -47281,7 +47281,7 @@
         <v>46124.38353318287</v>
       </c>
       <c r="D84" s="1">
-        <v>46124.63349537037</v>
+        <v>46124.38349537037</v>
       </c>
       <c r="E84">
         <v>18907</v>
@@ -47403,7 +47403,7 @@
         <v>46124.38352861111</v>
       </c>
       <c r="D85" s="1">
-        <v>46124.63350694445</v>
+        <v>46124.38350694445</v>
       </c>
       <c r="E85">
         <v>18927</v>
@@ -47546,7 +47546,7 @@
         <v>46124.383874618055</v>
       </c>
       <c r="D86" s="1">
-        <v>46124.63384259259</v>
+        <v>46124.38384259259</v>
       </c>
       <c r="E86">
         <v>18149</v>
@@ -47668,7 +47668,7 @@
         <v>46124.38387560185</v>
       </c>
       <c r="D87" s="1">
-        <v>46124.63385416667</v>
+        <v>46124.38385416667</v>
       </c>
       <c r="E87">
         <v>18169</v>
@@ -47811,7 +47811,7 @@
         <v>46124.38421863426</v>
       </c>
       <c r="D88" s="1">
-        <v>46124.63418981482</v>
+        <v>46124.38418981482</v>
       </c>
       <c r="E88">
         <v>17391</v>
@@ -47933,7 +47933,7 @@
         <v>46124.38422371528</v>
       </c>
       <c r="D89" s="1">
-        <v>46124.634201388886</v>
+        <v>46124.384201388886</v>
       </c>
       <c r="E89">
         <v>17414</v>
@@ -48076,7 +48076,7 @@
         <v>46124.3845640625</v>
       </c>
       <c r="D90" s="1">
-        <v>46124.63453703704</v>
+        <v>46124.38453703704</v>
       </c>
       <c r="E90">
         <v>16679</v>
@@ -48198,7 +48198,7 @@
         <v>46124.38491584491</v>
       </c>
       <c r="D91" s="1">
-        <v>46124.634884259256</v>
+        <v>46124.384884259256</v>
       </c>
       <c r="E91">
         <v>15973</v>
@@ -48320,7 +48320,7 @@
         <v>46124.384917881944</v>
       </c>
       <c r="D92" s="1">
-        <v>46124.63489583333</v>
+        <v>46124.38489583333</v>
       </c>
       <c r="E92">
         <v>16005</v>
@@ -48463,7 +48463,7 @@
         <v>46124.385262523145</v>
       </c>
       <c r="D93" s="1">
-        <v>46124.63523148148</v>
+        <v>46124.38523148148</v>
       </c>
       <c r="E93">
         <v>15268</v>
@@ -48585,7 +48585,7 @@
         <v>46124.38560688657</v>
       </c>
       <c r="D94" s="1">
-        <v>46124.6355787037</v>
+        <v>46124.3855787037</v>
       </c>
       <c r="E94">
         <v>14582</v>
@@ -48707,7 +48707,7 @@
         <v>46124.385964583336</v>
       </c>
       <c r="D95" s="1">
-        <v>46124.635925925926</v>
+        <v>46124.385925925926</v>
       </c>
       <c r="E95">
         <v>13893</v>
@@ -48829,7 +48829,7 @@
         <v>46124.38630211806</v>
       </c>
       <c r="D96" s="1">
-        <v>46124.63627314815</v>
+        <v>46124.38627314815</v>
       </c>
       <c r="E96">
         <v>13207</v>
@@ -48951,7 +48951,7 @@
         <v>46124.38664774306</v>
       </c>
       <c r="D97" s="1">
-        <v>46124.63662037037</v>
+        <v>46124.38662037037</v>
       </c>
       <c r="E97">
         <v>12544</v>
@@ -49073,7 +49073,7 @@
         <v>46124.38704193287</v>
       </c>
       <c r="D98" s="1">
-        <v>46124.636967592596</v>
+        <v>46124.386967592596</v>
       </c>
       <c r="E98">
         <v>11863</v>
@@ -49216,7 +49216,7 @@
         <v>46124.38699497685</v>
       </c>
       <c r="D99" s="1">
-        <v>46124.636967592596</v>
+        <v>46124.386967592596</v>
       </c>
       <c r="E99">
         <v>11891</v>
@@ -49338,7 +49338,7 @@
         <v>46124.38734253472</v>
       </c>
       <c r="D100" s="1">
-        <v>46124.63731481481</v>
+        <v>46124.38731481481</v>
       </c>
       <c r="E100">
         <v>11219</v>
@@ -49460,7 +49460,7 @@
         <v>46124.38770148148</v>
       </c>
       <c r="D101" s="1">
-        <v>46124.637662037036</v>
+        <v>46124.387662037036</v>
       </c>
       <c r="E101">
         <v>10589</v>
@@ -49582,7 +49582,7 @@
         <v>46124.3877943287</v>
       </c>
       <c r="D102" s="1">
-        <v>46124.63767361111</v>
+        <v>46124.38767361111</v>
       </c>
       <c r="E102">
         <v>10628</v>
@@ -49725,7 +49725,7 @@
         <v>46124.388048761575</v>
       </c>
       <c r="D103" s="1">
-        <v>46124.63800925926</v>
+        <v>46124.38800925926</v>
       </c>
       <c r="E103">
         <v>9972</v>
@@ -49847,7 +49847,7 @@
         <v>46124.38804913194</v>
       </c>
       <c r="D104" s="1">
-        <v>46124.638020833336</v>
+        <v>46124.388020833336</v>
       </c>
       <c r="E104">
         <v>10009</v>
@@ -49990,7 +49990,7 @@
         <v>46124.38838456019</v>
       </c>
       <c r="D105" s="1">
-        <v>46124.63835648148</v>
+        <v>46124.38835648148</v>
       </c>
       <c r="E105">
         <v>9355</v>
@@ -50112,7 +50112,7 @@
         <v>46124.38874392361</v>
       </c>
       <c r="D106" s="1">
-        <v>46124.638703703706</v>
+        <v>46124.388703703706</v>
       </c>
       <c r="E106">
         <v>8774</v>
@@ -50234,7 +50234,7 @@
         <v>46124.38874430556</v>
       </c>
       <c r="D107" s="1">
-        <v>46124.638715277775</v>
+        <v>46124.388715277775</v>
       </c>
       <c r="E107">
         <v>8814</v>
@@ -50377,7 +50377,7 @@
         <v>46124.389125636575</v>
       </c>
       <c r="D108" s="1">
-        <v>46124.63905092593</v>
+        <v>46124.38905092593</v>
       </c>
       <c r="E108">
         <v>8165</v>
@@ -50520,7 +50520,7 @@
         <v>46124.38907936343</v>
       </c>
       <c r="D109" s="1">
-        <v>46124.63905092593</v>
+        <v>46124.38905092593</v>
       </c>
       <c r="E109">
         <v>8190</v>
@@ -50642,7 +50642,7 @@
         <v>46124.3894265625</v>
       </c>
       <c r="D110" s="1">
-        <v>46124.639398148145</v>
+        <v>46124.389398148145</v>
       </c>
       <c r="E110">
         <v>7603</v>
@@ -50764,7 +50764,7 @@
         <v>46124.38980914352</v>
       </c>
       <c r="D111" s="1">
-        <v>46124.63974537037</v>
+        <v>46124.38974537037</v>
       </c>
       <c r="E111">
         <v>6991</v>
@@ -50907,7 +50907,7 @@
         <v>46124.389774270836</v>
       </c>
       <c r="D112" s="1">
-        <v>46124.63974537037</v>
+        <v>46124.38974537037</v>
       </c>
       <c r="E112">
         <v>7019</v>
@@ -51029,7 +51029,7 @@
         <v>46124.389785671294</v>
       </c>
       <c r="D113" s="1">
-        <v>46124.639756944445</v>
+        <v>46124.389756944445</v>
       </c>
       <c r="E113">
         <v>7053</v>
@@ -51172,7 +51172,7 @@
         <v>46124.39012186343</v>
       </c>
       <c r="D114" s="1">
-        <v>46124.64009259259</v>
+        <v>46124.39009259259</v>
       </c>
       <c r="E114">
         <v>6454</v>
@@ -51294,7 +51294,7 @@
         <v>46124.39013357639</v>
       </c>
       <c r="D115" s="1">
-        <v>46124.64010416667</v>
+        <v>46124.39010416667</v>
       </c>
       <c r="E115">
         <v>6497</v>
@@ -51437,7 +51437,7 @@
         <v>46124.390515659725</v>
       </c>
       <c r="D116" s="1">
-        <v>46124.640439814815</v>
+        <v>46124.390439814815</v>
       </c>
       <c r="E116">
         <v>5752</v>
@@ -51580,7 +51580,7 @@
         <v>46124.39048054398</v>
       </c>
       <c r="D117" s="1">
-        <v>46124.640439814815</v>
+        <v>46124.390439814815</v>
       </c>
       <c r="E117">
         <v>5788</v>
@@ -51702,7 +51702,7 @@
         <v>46124.39082803241</v>
       </c>
       <c r="D118" s="1">
-        <v>46124.64079861111</v>
+        <v>46124.39079861111</v>
       </c>
       <c r="E118">
         <v>5326</v>
@@ -51845,7 +51845,7 @@
         <v>46124.39117553241</v>
       </c>
       <c r="D119" s="1">
-        <v>46124.64113425926</v>
+        <v>46124.39113425926</v>
       </c>
       <c r="E119">
         <v>4843</v>
@@ -51967,7 +51967,7 @@
         <v>46124.39117623842</v>
       </c>
       <c r="D120" s="1">
-        <v>46124.64114583333</v>
+        <v>46124.39114583333</v>
       </c>
       <c r="E120">
         <v>4886</v>
@@ -52110,7 +52110,7 @@
         <v>46124.3915227662</v>
       </c>
       <c r="D121" s="1">
-        <v>46124.64148148148</v>
+        <v>46124.39148148148</v>
       </c>
       <c r="E121">
         <v>4610</v>
@@ -52232,7 +52232,7 @@
         <v>46124.39187034722</v>
       </c>
       <c r="D122" s="1">
-        <v>46124.6418287037</v>
+        <v>46124.3918287037</v>
       </c>
       <c r="E122">
         <v>4617</v>
